--- a/docs/テスト仕様書.xlsx
+++ b/docs/テスト仕様書.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="356">
   <si>
     <t>テスト仕様書</t>
   </si>
@@ -41,7 +41,7 @@
     <t>対象外</t>
   </si>
   <si>
-    <t>認証・権限機能（未実装）／ 複数端末での同時アクセス・排他制御（未実装） ／ 本番DB（MySQL等）を用いた永続化テスト（現状はH2インメモリのみ）</t>
+    <t>認証・権限機能（未実装）／ 複数端末での同時アクセス・排他制御（未実装）／ 本番相当の負荷・性能テスト</t>
   </si>
   <si>
     <t>■ テスト環境</t>
@@ -50,7 +50,7 @@
     <t>起動コマンド</t>
   </si>
   <si>
-    <t>.\gradlew.bat bootRun</t>
+    <t>.\gradlew.bat bootRun　※事前にPostgreSQLの起動とDB作成が必要（README.md参照）</t>
   </si>
   <si>
     <t>画面アクセスURL</t>
@@ -62,19 +62,19 @@
     <t>DB</t>
   </si>
   <si>
-    <t>H2インメモリ（jdbc:h2:mem:practicedb）。起動のたびにdata.sqlで初期化される</t>
-  </si>
-  <si>
-    <t>H2コンソール</t>
-  </si>
-  <si>
-    <t>http://localhost:8080/h2-console （JDBC URL: jdbc:h2:mem:practicedb, ユーザー: sa, パスワード: 空欄）</t>
+    <t>PostgreSQL（本番想定。jdbc:postgresql://localhost:5432/beautypos）。Flywayでスキーマ管理し、データは永続化される（テストのみH2インメモリで完結）</t>
+  </si>
+  <si>
+    <t>接続コマンド</t>
+  </si>
+  <si>
+    <t>psql -U beautypos_user -d beautypos　（または pgAdminで接続）</t>
   </si>
   <si>
     <t>初期データ</t>
   </si>
   <si>
-    <t>C001〜C006 の美容品6件（化粧水・美容液・口紅・ファンデーション・シャンプー・ネイルオイル）</t>
+    <t>Flywayマイグレーション V2__seed_data.sql により初回起動時のみ投入されるC001〜C006の美容品6件</t>
   </si>
   <si>
     <t>■ 実施方法・判定基準</t>
@@ -83,7 +83,7 @@
     <t>実施方法</t>
   </si>
   <si>
-    <t>ブラウザ操作を基本とし、API直接呼び出し（curl等）が必要なケースはテスト項目に明記する。DB確認が必要なケースはH2コンソールで直接テーブルを参照する</t>
+    <t>ブラウザ操作を基本とし、API直接呼び出し（curl等）が必要なケースはテスト項目に明記する。DB確認が必要なケースはpsql（またはpgAdmin）で直接テーブルを参照する</t>
   </si>
   <si>
     <t>判定基準</t>
@@ -119,25 +119,25 @@
     <t>0件／上限値／下限値など、境界となる値での挙動を確認するテスト（金色でハイライト）</t>
   </si>
   <si>
-    <t>■ 既知の未対応事項（実機テストで確認・確定した事項）</t>
+    <t>■ 過去に判明した不具合の対応状況（すべて解消済み）</t>
   </si>
   <si>
     <t>商品コード重複時のエラー処理</t>
   </si>
   <si>
-    <t>一意制約違反（重複barcode）に対する例外ハンドリングが未実装。現状はDB制約違反により500エラーとなる（画面・REST APIとも）。ITEM-005, ITEM-007, DB-009で実機確認済み</t>
+    <t>ITEM-005, ITEM-007で判明した重複コード・必須項目チェックの不備は2026-08-25に修正済み（DuplicateBarcodeException新設、ItemPageControllerへ@Valid追加）。バグ修正.xlsx参照。PostgreSQL環境でも2026-08-26に再確認しOK</t>
   </si>
   <si>
     <t>商品管理画面（Thymeleaf）の入力チェック</t>
   </si>
   <si>
-    <t>ItemPageControllerに @Valid が付与されておらず、サーバー側の入力チェックはブラウザのHTML5属性（required, min）に依存している。回避して不正値を送信した場合はDB保存時のBean Validationにより500エラーとなる</t>
+    <t>2026-08-25の修正によりItemPageControllerに@Validが付与され、サーバー側の入力チェックが有効化された（対応済み）</t>
   </si>
   <si>
     <t>レジ画面のクイック追加：空欄入力時の案内が表示されない</t>
   </si>
   <si>
-    <t>テキストボックスに required 属性があり、「カートに追加」ボタンに formnovalidate が無いため、空欄のまま押してもブラウザのHTML5必須チェックで送信がブロックされる。そのため実装済みのサーバー側エラーメッセージ（「商品コードまたは商品名を入力してください」）が実際の画面操作では表示されない。POS-005で実機確認済み（新規判明）</t>
+    <t>POS-005で判明した不具合（formnovalidate未設定）は2026-08-25に修正済み（pos.htmlのボタンにformnovalidateを追加）。PostgreSQL環境でも2026-08-26に再確認しOK（新規判明ではなく解消済み）</t>
   </si>
   <si>
     <t>■ テスト実施結果サマリ</t>
@@ -146,429 +146,432 @@
     <t>実施日</t>
   </si>
   <si>
+    <t>2026-08-26（PostgreSQL移行後の再実施）</t>
+  </si>
+  <si>
+    <t>実施者</t>
+  </si>
+  <si>
+    <t>Claude Code</t>
+  </si>
+  <si>
+    <t>実施結果</t>
+  </si>
+  <si>
+    <t>全48件中 OK: 48件 / NG: 0件（旧環境(H2)で確認された3件のNG(ITEM-005, ITEM-007, POS-005)は2026-08-25の修正で解消済み。今回PostgreSQL環境で全件再実施し、新たな不具合は無いことを確認）</t>
+  </si>
+  <si>
+    <t>エビデンス</t>
+  </si>
+  <si>
+    <t>実施ログ（curl／psqlコマンド出力）は テスト結果.xlsx を参照。DB整合性の確認はpsqlコマンドで実施（H2コンソールは使用しない）</t>
+  </si>
+  <si>
+    <t>商品管理機能 テストケース</t>
+  </si>
+  <si>
+    <t>商品マスタの画面（/items）と REST API（/api/items）の両方を対象とする</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>テストID</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>テスト項目</t>
+  </si>
+  <si>
+    <t>事前条件</t>
+  </si>
+  <si>
+    <t>手順</t>
+  </si>
+  <si>
+    <t>入力値</t>
+  </si>
+  <si>
+    <t>期待結果（画面／API）</t>
+  </si>
+  <si>
+    <t>期待結果（DB）</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>結果(OK/NG)</t>
+  </si>
+  <si>
+    <t>ITEM-001</t>
+  </si>
+  <si>
+    <t>商品一覧表示</t>
+  </si>
+  <si>
+    <t>初期データが投入済み</t>
+  </si>
+  <si>
+    <t>/items にアクセスする</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>商品一覧が表示される（商品コード・商品名・価格・在庫）。初期データ6件を含む</t>
+  </si>
+  <si>
+    <t>変更なし</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>ITEM-002</t>
+  </si>
+  <si>
+    <t>商品新規登録（画面）</t>
+  </si>
+  <si>
+    <t>/items/new を開いている</t>
+  </si>
+  <si>
+    <t>項目を入力して「保存」を押す</t>
+  </si>
+  <si>
+    <t>barcode=C010, name=リップグロス, price=1600, stock=12</t>
+  </si>
+  <si>
+    <t>一覧に新しい商品が追加される</t>
+  </si>
+  <si>
+    <t>ITEM テーブルに1行 INSERT される（IDは自動採番）</t>
+  </si>
+  <si>
+    <t>ITEM-003</t>
+  </si>
+  <si>
+    <t>商品編集（画面）</t>
+  </si>
+  <si>
+    <t>対象商品が存在する</t>
+  </si>
+  <si>
+    <t>「編集」→内容変更→「保存」</t>
+  </si>
+  <si>
+    <t>price=2000 に変更</t>
+  </si>
+  <si>
+    <t>一覧の該当行が更新された内容で表示される</t>
+  </si>
+  <si>
+    <t>ITEM テーブルの該当行が UPDATE される（IDは不変）</t>
+  </si>
+  <si>
+    <t>ITEM-004</t>
+  </si>
+  <si>
+    <t>商品削除（画面）</t>
+  </si>
+  <si>
+    <t>「削除」→確認ダイアログでOK</t>
+  </si>
+  <si>
+    <t>一覧から該当商品が消える</t>
+  </si>
+  <si>
+    <t>ITEM テーブルから該当行が DELETE される</t>
+  </si>
+  <si>
+    <t>ITEM-005</t>
+  </si>
+  <si>
+    <t>商品コード重複登録（画面）</t>
+  </si>
+  <si>
+    <t>既存の商品コード（例:C001）がある</t>
+  </si>
+  <si>
+    <t>新規登録フォームに既存と同じコードを入力して保存</t>
+  </si>
+  <si>
+    <t>barcode=C001（重複）</t>
+  </si>
+  <si>
+    <t>「この商品コードは既に使用されています: C001」等のエラーメッセージが表示され、登録フォーム画面に留まる（DuplicateBarcodeExceptionとして適切にハンドリングされる）</t>
+  </si>
+  <si>
+    <t>INSERT は行われない（一意制約違反でロールバック）</t>
+  </si>
+  <si>
+    <t>2026-08-25にDuplicateBarcodeExceptionを新設し修正済み（バグ修正.xlsx参照）。2026-08-26にPostgreSQL環境で再実施しOKを確認</t>
+  </si>
+  <si>
+    <t>ITEM-006</t>
+  </si>
+  <si>
+    <t>必須項目未入力（ブラウザ経由）</t>
+  </si>
+  <si>
+    <t>新規登録フォームを開いている</t>
+  </si>
+  <si>
+    <t>商品名を空欄のまま「保存」を押す</t>
+  </si>
+  <si>
+    <t>name=""</t>
+  </si>
+  <si>
+    <t>ブラウザのHTML5必須チェックにより送信がブロックされ、入力を促すメッセージが表示される</t>
+  </si>
+  <si>
+    <t>ITEM-007</t>
+  </si>
+  <si>
+    <t>必須項目未入力（サーバー直送）</t>
+  </si>
+  <si>
+    <t>curl等でHTML検証を回避してPOSTできる</t>
+  </si>
+  <si>
+    <t>POST /items に name を含めずに送信</t>
+  </si>
+  <si>
+    <t>name 省略</t>
+  </si>
+  <si>
+    <t>@Valid による入力チェックが有効なため、フォーム画面に「商品名を入力してください」等のエラーメッセージが表示される（200、DB更新なし）</t>
+  </si>
+  <si>
+    <t>INSERT されない</t>
+  </si>
+  <si>
+    <t>2026-08-25にItemPageControllerへ@Validを追加し修正済み（バグ修正.xlsx参照）。2026-08-26にPostgreSQL環境で再実施しOKを確認</t>
+  </si>
+  <si>
+    <t>ITEM-008</t>
+  </si>
+  <si>
+    <t>価格・在庫に0を指定</t>
+  </si>
+  <si>
+    <t>price=0, stock=0 を入力して保存</t>
+  </si>
+  <si>
+    <t>price=0, stock=0</t>
+  </si>
+  <si>
+    <t>登録できる（@Min(0)は0を許可するため）</t>
+  </si>
+  <si>
+    <t>ITEM に price=0, stock=0 で INSERT される</t>
+  </si>
+  <si>
+    <t>ITEM-009</t>
+  </si>
+  <si>
+    <t>価格に負数を指定（REST API）</t>
+  </si>
+  <si>
+    <t>POST /api/items に負の価格を指定</t>
+  </si>
+  <si>
+    <t>price=-100</t>
+  </si>
+  <si>
+    <t>400 Bad Request（バリデーションエラー）が返る</t>
+  </si>
+  <si>
+    <t>@Valid による入力チェックが有効</t>
+  </si>
+  <si>
+    <t>ITEM-010</t>
+  </si>
+  <si>
+    <t>REST API：一覧取得</t>
+  </si>
+  <si>
+    <t>GET /api/items</t>
+  </si>
+  <si>
+    <t>200 OK。barcode を含む商品一覧がJSONで返る</t>
+  </si>
+  <si>
+    <t>ITEM-011</t>
+  </si>
+  <si>
+    <t>REST API：新規登録</t>
+  </si>
+  <si>
+    <t>POST /api/items に正しいJSONを送信</t>
+  </si>
+  <si>
+    <t>barcode, name, price, stock</t>
+  </si>
+  <si>
+    <t>201 Created。登録内容がJSONで返る</t>
+  </si>
+  <si>
+    <t>ITEM に1行 INSERT される</t>
+  </si>
+  <si>
+    <t>ITEM-012</t>
+  </si>
+  <si>
+    <t>REST API：更新</t>
+  </si>
+  <si>
+    <t>対象IDが存在する</t>
+  </si>
+  <si>
+    <t>PUT /api/items/{id}</t>
+  </si>
+  <si>
+    <t>変更後の name/price/stock</t>
+  </si>
+  <si>
+    <t>200 OK。更新後の内容が返る</t>
+  </si>
+  <si>
+    <t>ITEM の該当行が UPDATE される</t>
+  </si>
+  <si>
+    <t>ITEM-013</t>
+  </si>
+  <si>
+    <t>REST API：削除</t>
+  </si>
+  <si>
+    <t>DELETE /api/items/{id}</t>
+  </si>
+  <si>
+    <t>204 No Content</t>
+  </si>
+  <si>
+    <t>ITEM の該当行が DELETE される</t>
+  </si>
+  <si>
+    <t>ITEM-014</t>
+  </si>
+  <si>
+    <t>存在しないIDの取得／更新／削除</t>
+  </si>
+  <si>
+    <t>GET, PUT, DELETE /api/items/9999</t>
+  </si>
+  <si>
+    <t>id=9999（存在しない）</t>
+  </si>
+  <si>
+    <t>404 Not Found（ItemNotFoundException）</t>
+  </si>
+  <si>
+    <t>レジ機能（POS）テストケース</t>
+  </si>
+  <si>
+    <t>商品検索・カート・支払い・会計確定（DB登録更新を含む）を対象とする</t>
+  </si>
+  <si>
+    <t>POS-001</t>
+  </si>
+  <si>
+    <t>クイック追加（商品コード）</t>
+  </si>
+  <si>
+    <t>カートが空</t>
+  </si>
+  <si>
+    <t>テキストボックスに商品コードを入力し「カートに追加」</t>
+  </si>
+  <si>
+    <t>keyword=C001</t>
+  </si>
+  <si>
+    <t>検索・選択なしでカートに「化粧水」が1点追加され、合計金額が更新される</t>
+  </si>
+  <si>
+    <t>DBへの書き込みは無い（カートはセッション上のみで保持）</t>
+  </si>
+  <si>
+    <t>POS-002</t>
+  </si>
+  <si>
+    <t>クイック追加の数量累積</t>
+  </si>
+  <si>
+    <t>C001が既にカートに1点ある</t>
+  </si>
+  <si>
+    <t>同じコードで再度クイック追加</t>
+  </si>
+  <si>
+    <t>keyword=C001（2回目）</t>
+  </si>
+  <si>
+    <t>新しい行は増えず、既存行の数量が2に加算される</t>
+  </si>
+  <si>
+    <t>POS-003</t>
+  </si>
+  <si>
+    <t>商品名でのクイック追加</t>
+  </si>
+  <si>
+    <t>商品名の一部でクイック追加</t>
+  </si>
+  <si>
+    <t>keyword=口紅</t>
+  </si>
+  <si>
+    <t>名称の部分一致で該当商品がカートに1点追加される</t>
+  </si>
+  <si>
+    <t>POS-004</t>
+  </si>
+  <si>
+    <t>存在しないコードでクイック追加</t>
+  </si>
+  <si>
+    <t>テキストボックスに存在しない値を入力し「カートに追加」</t>
+  </si>
+  <si>
+    <t>keyword=ZZZZ</t>
+  </si>
+  <si>
+    <t>「商品が見つかりません: ZZZZ」が画面に表示される</t>
+  </si>
+  <si>
+    <t>POS-005</t>
+  </si>
+  <si>
+    <t>空欄でクイック追加</t>
+  </si>
+  <si>
+    <t>テキストボックスを空欄のまま「カートに追加」</t>
+  </si>
+  <si>
+    <t>keyword=""</t>
+  </si>
+  <si>
+    <t>「商品コードまたは商品名を入力してください」が表示される</t>
+  </si>
+  <si>
+    <t>2026-08-25にpos.htmlの「カートに追加」ボタンへformnovalidateを追加し修正済み（バグ修正.xlsx参照）。2026-08-26にPostgreSQL環境で再実施し、案内メッセージが正しく表示されることを確認（OK）</t>
+  </si>
+  <si>
     <t>2026-08-25</t>
   </si>
   <si>
-    <t>実施者</t>
-  </si>
-  <si>
-    <t>Claude Code</t>
-  </si>
-  <si>
-    <t>実施結果</t>
-  </si>
-  <si>
-    <t>全48件中 OK: 45件 / NG: 3件（NG内容は上記「既知の未対応事項」を参照。今回はプログラム改修せずNGのまま記録）</t>
-  </si>
-  <si>
-    <t>エビデンス</t>
-  </si>
-  <si>
-    <t>画面キャプチャは test-evidence.xlsx を参照</t>
-  </si>
-  <si>
-    <t>商品管理機能 テストケース</t>
-  </si>
-  <si>
-    <t>商品マスタの画面（/items）と REST API（/api/items）の両方を対象とする</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>テストID</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
-    <t>テスト項目</t>
-  </si>
-  <si>
-    <t>事前条件</t>
-  </si>
-  <si>
-    <t>手順</t>
-  </si>
-  <si>
-    <t>入力値</t>
-  </si>
-  <si>
-    <t>期待結果（画面／API）</t>
-  </si>
-  <si>
-    <t>期待結果（DB）</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
-    <t>結果(OK/NG)</t>
-  </si>
-  <si>
-    <t>ITEM-001</t>
-  </si>
-  <si>
-    <t>商品一覧表示</t>
-  </si>
-  <si>
-    <t>初期データが投入済み</t>
-  </si>
-  <si>
-    <t>/items にアクセスする</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>商品一覧が表示される（商品コード・商品名・価格・在庫）。初期データ6件を含む</t>
-  </si>
-  <si>
-    <t>変更なし</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>ITEM-002</t>
-  </si>
-  <si>
-    <t>商品新規登録（画面）</t>
-  </si>
-  <si>
-    <t>/items/new を開いている</t>
-  </si>
-  <si>
-    <t>項目を入力して「保存」を押す</t>
-  </si>
-  <si>
-    <t>barcode=C010, name=リップグロス, price=1600, stock=12</t>
-  </si>
-  <si>
-    <t>一覧に新しい商品が追加される</t>
-  </si>
-  <si>
-    <t>ITEM テーブルに1行 INSERT される（IDは自動採番）</t>
-  </si>
-  <si>
-    <t>ITEM-003</t>
-  </si>
-  <si>
-    <t>商品編集（画面）</t>
-  </si>
-  <si>
-    <t>対象商品が存在する</t>
-  </si>
-  <si>
-    <t>「編集」→内容変更→「保存」</t>
-  </si>
-  <si>
-    <t>price=2000 に変更</t>
-  </si>
-  <si>
-    <t>一覧の該当行が更新された内容で表示される</t>
-  </si>
-  <si>
-    <t>ITEM テーブルの該当行が UPDATE される（IDは不変）</t>
-  </si>
-  <si>
-    <t>ITEM-004</t>
-  </si>
-  <si>
-    <t>商品削除（画面）</t>
-  </si>
-  <si>
-    <t>「削除」→確認ダイアログでOK</t>
-  </si>
-  <si>
-    <t>一覧から該当商品が消える</t>
-  </si>
-  <si>
-    <t>ITEM テーブルから該当行が DELETE される</t>
-  </si>
-  <si>
-    <t>ITEM-005</t>
-  </si>
-  <si>
-    <t>商品コード重複登録（画面）</t>
-  </si>
-  <si>
-    <t>既存の商品コード（例:C001）がある</t>
-  </si>
-  <si>
-    <t>新規登録フォームに既存と同じコードを入力して保存</t>
-  </si>
-  <si>
-    <t>barcode=C001（重複）</t>
-  </si>
-  <si>
-    <t>現状は例外未処理のため500エラー画面が表示される</t>
-  </si>
-  <si>
-    <t>INSERT は行われない（一意制約違反でロールバック）</t>
-  </si>
-  <si>
-    <t>【実施結果】想定どおり500エラー画面となることを実機で確認。既知の未対応事項のため今回はプログラム改修せずNGのまま記録（概要シート参照）</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>ITEM-006</t>
-  </si>
-  <si>
-    <t>必須項目未入力（ブラウザ経由）</t>
-  </si>
-  <si>
-    <t>新規登録フォームを開いている</t>
-  </si>
-  <si>
-    <t>商品名を空欄のまま「保存」を押す</t>
-  </si>
-  <si>
-    <t>name=""</t>
-  </si>
-  <si>
-    <t>ブラウザのHTML5必須チェックにより送信がブロックされ、入力を促すメッセージが表示される</t>
-  </si>
-  <si>
-    <t>ITEM-007</t>
-  </si>
-  <si>
-    <t>必須項目未入力（サーバー直送）</t>
-  </si>
-  <si>
-    <t>curl等でHTML検証を回避してPOSTできる</t>
-  </si>
-  <si>
-    <t>POST /items に name を含めずに送信</t>
-  </si>
-  <si>
-    <t>name 省略</t>
-  </si>
-  <si>
-    <t>サーバー側の入力チェックが無いため、DB保存時のBean Validationで例外が発生し500エラーとなる</t>
-  </si>
-  <si>
-    <t>INSERT されない</t>
-  </si>
-  <si>
-    <t>【実施結果】想定どおり500エラーとなることをAPI直接呼び出しで確認。既知の未対応事項のため今回はプログラム改修せずNGのまま記録（概要シート参照）</t>
-  </si>
-  <si>
-    <t>ITEM-008</t>
-  </si>
-  <si>
-    <t>価格・在庫に0を指定</t>
-  </si>
-  <si>
-    <t>price=0, stock=0 を入力して保存</t>
-  </si>
-  <si>
-    <t>price=0, stock=0</t>
-  </si>
-  <si>
-    <t>登録できる（@Min(0)は0を許可するため）</t>
-  </si>
-  <si>
-    <t>ITEM に price=0, stock=0 で INSERT される</t>
-  </si>
-  <si>
-    <t>ITEM-009</t>
-  </si>
-  <si>
-    <t>価格に負数を指定（REST API）</t>
-  </si>
-  <si>
-    <t>POST /api/items に負の価格を指定</t>
-  </si>
-  <si>
-    <t>price=-100</t>
-  </si>
-  <si>
-    <t>400 Bad Request（バリデーションエラー）が返る</t>
-  </si>
-  <si>
-    <t>@Valid による入力チェックが有効</t>
-  </si>
-  <si>
-    <t>ITEM-010</t>
-  </si>
-  <si>
-    <t>REST API：一覧取得</t>
-  </si>
-  <si>
-    <t>GET /api/items</t>
-  </si>
-  <si>
-    <t>200 OK。barcode を含む商品一覧がJSONで返る</t>
-  </si>
-  <si>
-    <t>ITEM-011</t>
-  </si>
-  <si>
-    <t>REST API：新規登録</t>
-  </si>
-  <si>
-    <t>POST /api/items に正しいJSONを送信</t>
-  </si>
-  <si>
-    <t>barcode, name, price, stock</t>
-  </si>
-  <si>
-    <t>201 Created。登録内容がJSONで返る</t>
-  </si>
-  <si>
-    <t>ITEM に1行 INSERT される</t>
-  </si>
-  <si>
-    <t>ITEM-012</t>
-  </si>
-  <si>
-    <t>REST API：更新</t>
-  </si>
-  <si>
-    <t>対象IDが存在する</t>
-  </si>
-  <si>
-    <t>PUT /api/items/{id}</t>
-  </si>
-  <si>
-    <t>変更後の name/price/stock</t>
-  </si>
-  <si>
-    <t>200 OK。更新後の内容が返る</t>
-  </si>
-  <si>
-    <t>ITEM の該当行が UPDATE される</t>
-  </si>
-  <si>
-    <t>ITEM-013</t>
-  </si>
-  <si>
-    <t>REST API：削除</t>
-  </si>
-  <si>
-    <t>DELETE /api/items/{id}</t>
-  </si>
-  <si>
-    <t>204 No Content</t>
-  </si>
-  <si>
-    <t>ITEM の該当行が DELETE される</t>
-  </si>
-  <si>
-    <t>ITEM-014</t>
-  </si>
-  <si>
-    <t>存在しないIDの取得／更新／削除</t>
-  </si>
-  <si>
-    <t>GET, PUT, DELETE /api/items/9999</t>
-  </si>
-  <si>
-    <t>id=9999（存在しない）</t>
-  </si>
-  <si>
-    <t>404 Not Found（ItemNotFoundException）</t>
-  </si>
-  <si>
-    <t>レジ機能（POS）テストケース</t>
-  </si>
-  <si>
-    <t>商品検索・カート・支払い・会計確定（DB登録更新を含む）を対象とする</t>
-  </si>
-  <si>
-    <t>POS-001</t>
-  </si>
-  <si>
-    <t>クイック追加（商品コード）</t>
-  </si>
-  <si>
-    <t>カートが空</t>
-  </si>
-  <si>
-    <t>テキストボックスに商品コードを入力し「カートに追加」</t>
-  </si>
-  <si>
-    <t>keyword=C001</t>
-  </si>
-  <si>
-    <t>検索・選択なしでカートに「化粧水」が1点追加され、合計金額が更新される</t>
-  </si>
-  <si>
-    <t>DBへの書き込みは無い（カートはセッション上のみで保持）</t>
-  </si>
-  <si>
-    <t>POS-002</t>
-  </si>
-  <si>
-    <t>クイック追加の数量累積</t>
-  </si>
-  <si>
-    <t>C001が既にカートに1点ある</t>
-  </si>
-  <si>
-    <t>同じコードで再度クイック追加</t>
-  </si>
-  <si>
-    <t>keyword=C001（2回目）</t>
-  </si>
-  <si>
-    <t>新しい行は増えず、既存行の数量が2に加算される</t>
-  </si>
-  <si>
-    <t>POS-003</t>
-  </si>
-  <si>
-    <t>商品名でのクイック追加</t>
-  </si>
-  <si>
-    <t>商品名の一部でクイック追加</t>
-  </si>
-  <si>
-    <t>keyword=口紅</t>
-  </si>
-  <si>
-    <t>名称の部分一致で該当商品がカートに1点追加される</t>
-  </si>
-  <si>
-    <t>POS-004</t>
-  </si>
-  <si>
-    <t>存在しないコードでクイック追加</t>
-  </si>
-  <si>
-    <t>テキストボックスに存在しない値を入力し「カートに追加」</t>
-  </si>
-  <si>
-    <t>keyword=ZZZZ</t>
-  </si>
-  <si>
-    <t>「商品が見つかりません: ZZZZ」が画面に表示される</t>
-  </si>
-  <si>
-    <t>POS-005</t>
-  </si>
-  <si>
-    <t>空欄でクイック追加</t>
-  </si>
-  <si>
-    <t>テキストボックスを空欄のまま「カートに追加」</t>
-  </si>
-  <si>
-    <t>keyword=""</t>
-  </si>
-  <si>
-    <t>「商品コードまたは商品名を入力してください」が表示される</t>
-  </si>
-  <si>
-    <t>【実施結果】新規に判明した不具合。テキストボックスに required 属性があり、「カートに追加」ボタンに formnovalidate が無いため、空欄では送信自体がブラウザのHTML5バリデーションでブロックされ、サーバーに届かない。そのため本来表示されるはずの案内メッセージが実際には表示されない（直前の画面表示が残る）。プログラム改修は未実施でNGのまま記録</t>
-  </si>
-  <si>
     <t>POS-006</t>
   </si>
   <si>
@@ -878,6 +881,9 @@
     <t>「まだ売上がありません」等の空状態メッセージが表示される</t>
   </si>
   <si>
+    <t>PostgreSQLはデータが永続化されるため、実データを保持したまま「売上0件」の状態を再現するにはテーブルの初期化が必要。既存データ保護のため今回は未実施（H2環境での実施結果を維持）</t>
+  </si>
+  <si>
     <t>SALES-003</t>
   </si>
   <si>
@@ -893,7 +899,7 @@
     <t>DB整合性・データ確認 テストケース</t>
   </si>
   <si>
-    <t>H2コンソール（/h2-console）および起動ログを用いて、テーブル構造とデータの整合性を確認する</t>
+    <t>psql（またはpgAdmin）とFlywayマイグレーション履歴（flyway_schema_history）を用いて、テーブル構造とデータの整合性を確認する</t>
   </si>
   <si>
     <t>DB-001</t>
@@ -905,10 +911,10 @@
     <t>アプリを起動した直後</t>
   </si>
   <si>
-    <t>H2コンソールで ITEM テーブルを SELECT する</t>
-  </si>
-  <si>
-    <t>SELECT * FROM ITEM</t>
+    <t>psqlで item テーブルを SELECT する</t>
+  </si>
+  <si>
+    <t>SELECT * FROM item;</t>
   </si>
   <si>
     <t>data.sql の6商品（C001〜C006）が登録されている</t>
@@ -920,19 +926,22 @@
     <t>DB-002</t>
   </si>
   <si>
-    <t>インメモリ特性の確認（再起動でリセット）</t>
+    <t>永続化の確認（再起動してもデータが保持される）</t>
   </si>
   <si>
     <t>商品を追加または会計を実施した後、アプリを再起動する</t>
   </si>
   <si>
-    <t>再起動後にITEM/SALEテーブルを確認する</t>
-  </si>
-  <si>
-    <t>追加した商品や会計履歴が消え、data.sqlの初期状態に戻る</t>
-  </si>
-  <si>
-    <t>ddl-auto=create-drop のため起動のたびにテーブルが再作成される</t>
+    <t>再起動後に psql で item / sale テーブルを確認する</t>
+  </si>
+  <si>
+    <t>追加した商品や会計履歴は消えず、再起動前の状態のまま保持されている</t>
+  </si>
+  <si>
+    <t>PostgreSQLは永続DBのため、ddl-auto=validateであり再起動してもテーブル・データは変化しない（Flywayも "Schema is up to date" となり再適用されない）</t>
+  </si>
+  <si>
+    <t>H2環境では逆の結果（再起動でリセット）が期待値だったが、PostgreSQL移行により永続化される仕様に変更。2026-08-26に実機で再起動しitem/saleの内容が完全一致することを確認</t>
   </si>
   <si>
     <t>DB-003</t>
@@ -944,13 +953,16 @@
     <t>アプリを起動する</t>
   </si>
   <si>
-    <t>起動ログの DDL（create table）を確認する</t>
+    <t>flyway_schema_history テーブルの内容、および psql の \dt を確認する</t>
+  </si>
+  <si>
+    <t>\dt</t>
   </si>
   <si>
     <t>ITEM／SALE／SALE_ITEM の3テーブルが作成される</t>
   </si>
   <si>
-    <t>各テーブルのカラム構成がエンティティ定義と一致する</t>
+    <t>各テーブルのカラム構成が V1__init_schema.sql のCREATE TABLE定義と一致する</t>
   </si>
   <si>
     <t>DB-004</t>
@@ -959,13 +971,16 @@
     <t>外部キー制約の確認（SALE_ITEM→SALE）</t>
   </si>
   <si>
-    <t>起動ログの alter table 文を確認する</t>
+    <t>psqlで \d sale_item を実行し、外部キー制約を確認する</t>
+  </si>
+  <si>
+    <t>\d sale_item</t>
   </si>
   <si>
     <t>SALE_ITEM.sale_id に SALE テーブルへの外部キー制約が付与されている</t>
   </si>
   <si>
-    <t>"add constraint ... foreign key (sale_id) references sale" の行で確認</t>
+    <t>V1__init_schema.sql内の "CONSTRAINT fk_sale_item_sale FOREIGN KEY (sale_id) REFERENCES sale (id)" に対応。psqlの出力でも制約名 "fk_sale_item_sale" として確認できる</t>
   </si>
   <si>
     <t>DB-005</t>
@@ -974,10 +989,7 @@
     <t>item_id にFK制約が無いことの確認</t>
   </si>
   <si>
-    <t>H2コンソールで SALE_ITEM テーブルの定義を確認する</t>
-  </si>
-  <si>
-    <t>SHOW COLUMNS FROM SALE_ITEM 等</t>
+    <t>psqlで \d sale_item を実行し、item_id列の定義を確認する</t>
   </si>
   <si>
     <t>item_id カラムには外部キー制約が無いことを確認する（意図的な設計）</t>
@@ -995,7 +1007,7 @@
     <t>対象商品を含む会計を1件済ませている</t>
   </si>
   <si>
-    <t>商品管理画面で対象商品の価格を変更した後、/salesおよびH2コンソールでSALE_ITEMを確認する</t>
+    <t>商品管理画面で対象商品の価格を変更した後、/sales および psql で sale_item を確認する</t>
   </si>
   <si>
     <t>商品の price を変更</t>
@@ -1016,10 +1028,10 @@
     <t>カートに商品を追加している</t>
   </si>
   <si>
-    <t>会計確定の直後にH2コンソールでITEM.stockを確認する</t>
-  </si>
-  <si>
-    <t>SELECT stock FROM ITEM WHERE barcode=...</t>
+    <t>会計確定の直後にpsqlで item.stock を確認する</t>
+  </si>
+  <si>
+    <t>SELECT stock FROM item WHERE barcode=...;</t>
   </si>
   <si>
     <t>/items 画面の在庫表示が減少している</t>
@@ -1037,7 +1049,7 @@
     <t>商品A(在庫十分)と商品B(在庫不足)をカートに入れている</t>
   </si>
   <si>
-    <t>会計確定を実行し、その後H2コンソールでSALE件数とITEM.stockを確認する</t>
+    <t>会計確定を実行し、その後psqlでsale件数とitem.stockを確認する</t>
   </si>
   <si>
     <t>A,B混在、Bが在庫不足</t>
@@ -1058,13 +1070,13 @@
     <t>ITEMに既存のbarcodeがある</t>
   </si>
   <si>
-    <t>H2コンソールで同じbarcodeのINSERT文を直接実行する</t>
-  </si>
-  <si>
-    <t>INSERT INTO ITEM (barcode,...) VALUES ('C001',...)</t>
-  </si>
-  <si>
-    <t>一意制約違反でエラーとなり、登録が拒否される</t>
+    <t>psqlで同じbarcodeのINSERT文を直接実行する</t>
+  </si>
+  <si>
+    <t>INSERT INTO item (barcode, name, price, stock) VALUES ('C001', 'dup-test', 100, 1);</t>
+  </si>
+  <si>
+    <t>一意制約違反（uk_item_barcode）でエラーとなり、登録が拒否される</t>
   </si>
   <si>
     <t>ITEMテーブルに重複行が作られないことを確認する</t>
@@ -1105,18 +1117,18 @@
     <font>
       <b/>
       <color rgb="FF4A3B3F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
       <color rgb="FF4A3B3F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
   </fonts>
@@ -2059,7 +2071,7 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="D40:I40"/>
   </mergeCells>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2069,7 +2081,7 @@
     <tabColor rgb="FFC9A961"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N18"/>
+  <dimension ref="B1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2088,6 +2100,7 @@
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>50</v>
@@ -2195,13 +2208,13 @@
         <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2209,40 +2222,40 @@
         <v>2</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2250,40 +2263,40 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2291,40 +2304,40 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2332,40 +2345,40 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2400,13 +2413,13 @@
         <v>70</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2441,13 +2454,13 @@
         <v>113</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2482,13 +2495,13 @@
         <v>70</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2523,13 +2536,13 @@
         <v>125</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2564,13 +2577,13 @@
         <v>70</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M14" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2605,13 +2618,13 @@
         <v>70</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2646,13 +2659,13 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2687,13 +2700,13 @@
         <v>70</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2728,13 +2741,13 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2742,7 +2755,7 @@
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2752,7 +2765,7 @@
     <tabColor rgb="FFD17A9C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N26"/>
+  <dimension ref="B1:N26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2771,6 +2784,7 @@
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>153</v>
@@ -2878,13 +2892,13 @@
         <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2919,13 +2933,13 @@
         <v>70</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -2960,13 +2974,13 @@
         <v>70</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3001,13 +3015,13 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3042,13 +3056,13 @@
         <v>183</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3056,25 +3070,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>181</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>69</v>
@@ -3083,13 +3097,13 @@
         <v>70</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3097,25 +3111,25 @@
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>67</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>69</v>
@@ -3124,13 +3138,13 @@
         <v>70</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3138,25 +3152,25 @@
         <v>8</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>69</v>
@@ -3165,13 +3179,13 @@
         <v>70</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3179,25 +3193,25 @@
         <v>9</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>69</v>
@@ -3206,13 +3220,13 @@
         <v>70</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3220,25 +3234,25 @@
         <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>176</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>69</v>
@@ -3247,13 +3261,13 @@
         <v>70</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M14" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3261,25 +3275,25 @@
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>69</v>
@@ -3288,13 +3302,13 @@
         <v>70</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3302,25 +3316,25 @@
         <v>12</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>69</v>
@@ -3329,13 +3343,13 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3343,25 +3357,25 @@
         <v>13</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>157</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>69</v>
@@ -3370,13 +3384,13 @@
         <v>70</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3384,25 +3398,25 @@
         <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>69</v>
@@ -3411,13 +3425,13 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3425,25 +3439,25 @@
         <v>15</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>69</v>
@@ -3452,13 +3466,13 @@
         <v>70</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M19" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3466,40 +3480,40 @@
         <v>16</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3507,40 +3521,40 @@
         <v>17</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3548,40 +3562,40 @@
         <v>18</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3589,40 +3603,40 @@
         <v>19</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3630,40 +3644,40 @@
         <v>20</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3671,25 +3685,25 @@
         <v>21</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>69</v>
@@ -3698,13 +3712,13 @@
         <v>70</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3712,40 +3726,40 @@
         <v>22</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K26" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3753,7 +3767,7 @@
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3763,7 +3777,7 @@
     <tabColor rgb="FFC9A961"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N7"/>
+  <dimension ref="B1:N7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3782,9 +3796,10 @@
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -3801,7 +3816,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3862,25 +3877,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>69</v>
@@ -3889,13 +3904,13 @@
         <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3903,40 +3918,40 @@
         <v>2</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>69</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -3944,25 +3959,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>69</v>
@@ -3971,13 +3986,13 @@
         <v>70</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +4000,7 @@
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3995,7 +4010,7 @@
     <tabColor rgb="FFD17A9C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N13"/>
+  <dimension ref="B1:N13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -4014,9 +4029,10 @@
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4033,7 +4049,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4094,40 +4110,40 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4135,40 +4151,40 @@
         <v>2</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4176,40 +4192,40 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>67</v>
+        <v>313</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4217,40 +4233,40 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>67</v>
+        <v>319</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>67</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4258,40 +4274,40 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>319</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>67</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4299,40 +4315,40 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4340,40 +4356,40 @@
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4381,40 +4397,40 @@
         <v>8</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>45</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -4422,40 +4438,40 @@
         <v>9</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -4463,6 +4479,6 @@
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>